--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="108">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240726120000</t>
+    <t>20241209120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-26T12:00:00+01:00</t>
+    <t>2024-12-09T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,6 +311,30 @@
   </si>
   <si>
     <t>Unité neuro-vasculaire (UNV) de recours</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Filière Obésité – Niveau 1 (Conventionné CSO)</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Filière Obésité – Niveau 2 (Conventionné CSO)</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Filière Obésité – Niveau 3 (Conventionné CSO)</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Filière Obésité – Niveau 3 (Centre Spécialisé Obésité)</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R344-NiveauExpertise/FHIR/TRE-R344-NiveauExpertise</t>
@@ -653,7 +677,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -902,18 +926,50 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>38</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B32" t="s" s="2">
-        <v>99</v>
+      <c r="B36" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
